--- a/groups.xlsx
+++ b/groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B79C7A3-2B3C-4AA3-B7AD-B33443810181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED429D5-D2D3-4D27-B502-714B764097E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="125">
   <si>
     <t>グループ名</t>
   </si>
@@ -503,6 +503,17 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>グ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>8W004849</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フレーム固定金具_G10</t>
+    <rPh sb="4" eb="8">
+      <t>コテイカナグ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -640,7 +651,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -945,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.5546875" bestFit="1" customWidth="1"/>
@@ -1347,21 +1358,21 @@
         <v>118</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" t="s">
-        <v>70</v>
+        <v>123</v>
+      </c>
+      <c r="C38">
+        <v>4400484</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1369,36 +1380,47 @@
         <v>122</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+    <row r="44" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>80</v>
       </c>
     </row>
